--- a/data/out/variants/v3_no_solar/raw_v3_no_solar.xlsx
+++ b/data/out/variants/v3_no_solar/raw_v3_no_solar.xlsx
@@ -526,19 +526,19 @@
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>0.4363940256764344</v>
+        <v>0.4363940256764356</v>
       </c>
       <c r="G2" t="n">
-        <v>215.7851889473627</v>
+        <v>215.7851889473623</v>
       </c>
       <c r="H2" t="n">
-        <v>141629.539532403</v>
+        <v>141629.5395324027</v>
       </c>
       <c r="I2" t="n">
-        <v>376.3370026085702</v>
+        <v>376.3370026085698</v>
       </c>
       <c r="J2" t="n">
-        <v>36.22486541141431</v>
+        <v>36.22486541141426</v>
       </c>
       <c r="K2" t="n">
         <v>48192</v>
@@ -550,7 +550,7 @@
         <v>9639</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0483546257019043</v>
+        <v>0.0366978645324707</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -580,19 +580,19 @@
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>0.4363773408754615</v>
+        <v>0.4363777439724796</v>
       </c>
       <c r="G3" t="n">
-        <v>215.7848917161826</v>
+        <v>215.7842916425894</v>
       </c>
       <c r="H3" t="n">
-        <v>141633.7322854727</v>
+        <v>141633.630990512</v>
       </c>
       <c r="I3" t="n">
-        <v>376.3425730441252</v>
+        <v>376.3424384659694</v>
       </c>
       <c r="J3" t="n">
-        <v>36.22288912017844</v>
+        <v>36.22262711927088</v>
       </c>
       <c r="K3" t="n">
         <v>48192</v>
@@ -604,7 +604,7 @@
         <v>9639</v>
       </c>
       <c r="N3" t="n">
-        <v>0.03719687461853027</v>
+        <v>0.02899813652038574</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -634,19 +634,19 @@
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>0.4169709579043718</v>
+        <v>0.4168726111707083</v>
       </c>
       <c r="G4" t="n">
-        <v>215.427830845733</v>
+        <v>215.0832681435666</v>
       </c>
       <c r="H4" t="n">
-        <v>146510.396496642</v>
+        <v>146535.1102208355</v>
       </c>
       <c r="I4" t="n">
-        <v>382.7667651411784</v>
+        <v>382.7990467867384</v>
       </c>
       <c r="J4" t="n">
-        <v>35.10774232450864</v>
+        <v>34.9887348244167</v>
       </c>
       <c r="K4" t="n">
         <v>48192</v>
@@ -658,7 +658,7 @@
         <v>9639</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8776473999023438</v>
+        <v>0.8557267189025879</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -692,19 +692,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.4156757028039308</v>
+        <v>0.415520441358744</v>
       </c>
       <c r="G5" t="n">
-        <v>212.549645638009</v>
+        <v>212.4638087394797</v>
       </c>
       <c r="H5" t="n">
-        <v>146835.8834357622</v>
+        <v>146874.8993582164</v>
       </c>
       <c r="I5" t="n">
-        <v>383.1917058546051</v>
+        <v>383.2426116159533</v>
       </c>
       <c r="J5" t="n">
-        <v>33.87183185401047</v>
+        <v>33.85008721056142</v>
       </c>
       <c r="K5" t="n">
         <v>48192</v>
@@ -716,7 +716,7 @@
         <v>9639</v>
       </c>
       <c r="N5" t="n">
-        <v>4.499079465866089</v>
+        <v>3.974992990493774</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>-164.9025554905195</v>
+        <v>-164.9426480233035</v>
       </c>
     </row>
     <row r="6">
@@ -755,7 +755,7 @@
         <v>-0.20242521933611</v>
       </c>
       <c r="G6" t="n">
-        <v>317.0142636730758</v>
+        <v>317.014263673076</v>
       </c>
       <c r="H6" t="n">
         <v>302159.5545382801</v>
@@ -764,7 +764,7 @@
         <v>549.6904169969494</v>
       </c>
       <c r="J6" t="n">
-        <v>42.96015843455148</v>
+        <v>42.96015843455152</v>
       </c>
       <c r="K6" t="n">
         <v>48192</v>
@@ -776,7 +776,7 @@
         <v>9639</v>
       </c>
       <c r="N6" t="n">
-        <v>1.335348606109619</v>
+        <v>1.319869995117188</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>-197.9457752961974</v>
+        <v>-199.2153675099386</v>
       </c>
     </row>
     <row r="7">
@@ -808,23 +808,23 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>{'max_depth': None, 'min_samples_split': 5, 'n_estimators': 100}</t>
+          <t>{'max_depth': 20, 'min_samples_split': 5, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.02802882147862285</v>
+        <v>0.02671179342292118</v>
       </c>
       <c r="G7" t="n">
-        <v>271.9935925407841</v>
+        <v>272.3910710673694</v>
       </c>
       <c r="H7" t="n">
-        <v>244248.3520831512</v>
+        <v>244579.310386608</v>
       </c>
       <c r="I7" t="n">
-        <v>494.2148845220581</v>
+        <v>494.5496035653128</v>
       </c>
       <c r="J7" t="n">
-        <v>37.01671490943486</v>
+        <v>37.13437977782546</v>
       </c>
       <c r="K7" t="n">
         <v>48192</v>
@@ -836,7 +836,7 @@
         <v>9639</v>
       </c>
       <c r="N7" t="n">
-        <v>360.8331985473633</v>
+        <v>360.4015421867371</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>-199.7835099550085</v>
+        <v>-199.7635324758198</v>
       </c>
     </row>
     <row r="8">
@@ -872,19 +872,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>-0.1213581120326102</v>
+        <v>-0.1196406928422507</v>
       </c>
       <c r="G8" t="n">
-        <v>312.9114660549058</v>
+        <v>312.8663800945411</v>
       </c>
       <c r="H8" t="n">
-        <v>281788.0581353214</v>
+        <v>281356.4848373153</v>
       </c>
       <c r="I8" t="n">
-        <v>530.8371295749021</v>
+        <v>530.4304712564272</v>
       </c>
       <c r="J8" t="n">
-        <v>48.60424319129994</v>
+        <v>48.41390484631408</v>
       </c>
       <c r="K8" t="n">
         <v>48192</v>
@@ -896,7 +896,7 @@
         <v>9639</v>
       </c>
       <c r="N8" t="n">
-        <v>360.0971863269806</v>
+        <v>270.1056146621704</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>-178.5023315514871</v>
+        <v>-179.0588559938952</v>
       </c>
     </row>
     <row r="9">
@@ -932,19 +932,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.1675969850489103</v>
+        <v>0.1591604853315668</v>
       </c>
       <c r="G9" t="n">
-        <v>273.8484781129118</v>
+        <v>276.9219372938908</v>
       </c>
       <c r="H9" t="n">
-        <v>209176.0220505126</v>
+        <v>211296.0449471234</v>
       </c>
       <c r="I9" t="n">
-        <v>457.3576522269116</v>
+        <v>459.6694953410803</v>
       </c>
       <c r="J9" t="n">
-        <v>67.0369413795983</v>
+        <v>68.24927346204443</v>
       </c>
       <c r="K9" t="n">
         <v>48192</v>
@@ -956,7 +956,7 @@
         <v>9639</v>
       </c>
       <c r="N9" t="n">
-        <v>558.6282529830933</v>
+        <v>175.9585692882538</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>-240.4407606238266</v>
+        <v>-239.7362440780039</v>
       </c>
     </row>
     <row r="10">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.3608603075450916</v>
+        <v>0.3588790906175692</v>
       </c>
       <c r="G10" t="n">
-        <v>234.6286296740919</v>
+        <v>231.9432561172617</v>
       </c>
       <c r="H10" t="n">
-        <v>160610.5408089629</v>
+        <v>161108.4043057003</v>
       </c>
       <c r="I10" t="n">
-        <v>400.7624493499396</v>
+        <v>401.3831141262675</v>
       </c>
       <c r="J10" t="n">
-        <v>61.07642573648086</v>
+        <v>60.49205984936214</v>
       </c>
       <c r="K10" t="n">
         <v>48192</v>
@@ -1016,7 +1016,7 @@
         <v>9639</v>
       </c>
       <c r="N10" t="n">
-        <v>6.088701963424683</v>
+        <v>1.692628622055054</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>-211.2782165377461</v>
+        <v>-210.6880675654296</v>
       </c>
     </row>
     <row r="11">
@@ -1048,23 +1048,23 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>{'n_estimators': 968, 'learning_rate': 0.05857627843208948, 'max_depth': 3, 'subsample': 0.8817985160787244, 'colsample_bytree': 0.826217647346337}</t>
+          <t>{'n_estimators': 845, 'learning_rate': 0.026705018740813623, 'max_depth': 3, 'subsample': 0.6715114066532244, 'colsample_bytree': 0.7446612360430744}</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>-0.08881181071697752</v>
+        <v>-0.01147654539373688</v>
       </c>
       <c r="G11" t="n">
-        <v>299.6852943985867</v>
+        <v>289.6760141513293</v>
       </c>
       <c r="H11" t="n">
-        <v>273609.4406635172</v>
+        <v>254175.7254150364</v>
       </c>
       <c r="I11" t="n">
-        <v>523.076897466823</v>
+        <v>504.158432851258</v>
       </c>
       <c r="J11" t="n">
-        <v>41.79295795674962</v>
+        <v>41.61551719333666</v>
       </c>
       <c r="K11" t="n">
         <v>48192</v>
@@ -1076,7 +1076,7 @@
         <v>9639</v>
       </c>
       <c r="N11" t="n">
-        <v>153.4087028503418</v>
+        <v>77.84484958648682</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1106,23 +1106,23 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>{'n_estimators': 688, 'learning_rate': 0.023265274108165375, 'num_leaves': 32, 'min_child_samples': 31}</t>
+          <t>{'n_estimators': 912, 'learning_rate': 0.015441429037092473, 'num_leaves': 50, 'min_child_samples': 47}</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>-0.02908798534053569</v>
+        <v>-0.04049361885776803</v>
       </c>
       <c r="G12" t="n">
-        <v>283.8285142815318</v>
+        <v>290.5020688656133</v>
       </c>
       <c r="H12" t="n">
-        <v>258601.3352272129</v>
+        <v>261467.47699418</v>
       </c>
       <c r="I12" t="n">
-        <v>508.5285982392858</v>
+        <v>511.3389062003595</v>
       </c>
       <c r="J12" t="n">
-        <v>39.03517078736115</v>
+        <v>43.61083984022405</v>
       </c>
       <c r="K12" t="n">
         <v>48192</v>
@@ -1134,7 +1134,7 @@
         <v>9639</v>
       </c>
       <c r="N12" t="n">
-        <v>519.5456731319427</v>
+        <v>192.2790906429291</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1164,23 +1164,23 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>{'iterations': 374, 'learning_rate': 0.07499024777789919, 'depth': 4}</t>
+          <t>{'iterations': 994, 'learning_rate': 0.017644832501924217, 'depth': 4}</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>-0.1496844249375797</v>
+        <v>-0.04710470878714101</v>
       </c>
       <c r="G13" t="n">
-        <v>312.5657443540689</v>
+        <v>295.6929788941306</v>
       </c>
       <c r="H13" t="n">
-        <v>288906.2272750232</v>
+        <v>263128.7894450073</v>
       </c>
       <c r="I13" t="n">
-        <v>537.4999788604863</v>
+        <v>512.9608069287626</v>
       </c>
       <c r="J13" t="n">
-        <v>45.1697850516891</v>
+        <v>41.69870015668158</v>
       </c>
       <c r="K13" t="n">
         <v>48192</v>
@@ -1192,7 +1192,7 @@
         <v>9639</v>
       </c>
       <c r="N13" t="n">
-        <v>352.6316735744476</v>
+        <v>133.8456287384033</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -1222,23 +1222,23 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 100}</t>
+          <t>{'max_depth': 20, 'min_samples_split': 2, 'n_estimators': 300}</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.3107821333652029</v>
+        <v>0.2737586543046721</v>
       </c>
       <c r="G14" t="n">
-        <v>240.2355858180308</v>
+        <v>250.0357247134153</v>
       </c>
       <c r="H14" t="n">
-        <v>173194.7735404089</v>
+        <v>182498.4689058171</v>
       </c>
       <c r="I14" t="n">
-        <v>416.1667616958482</v>
+        <v>427.1983952519217</v>
       </c>
       <c r="J14" t="n">
-        <v>53.55401516142837</v>
+        <v>55.39353205198393</v>
       </c>
       <c r="K14" t="n">
         <v>48192</v>
@@ -1250,7 +1250,7 @@
         <v>9639</v>
       </c>
       <c r="N14" t="n">
-        <v>266.2720539569855</v>
+        <v>76.22590684890747</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>-158.2656159153291</v>
+        <v>-161.1145510072703</v>
       </c>
     </row>
     <row r="15">
@@ -1310,7 +1310,7 @@
         <v>9639</v>
       </c>
       <c r="N15" t="n">
-        <v>53.05555987358093</v>
+        <v>15.2321674823761</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -1342,23 +1342,23 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>{'alpha': 0.01, 'hidden_layer_sizes': (64,), 'learning_rate_init': 0.0001}</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64,), 'learning_rate_init': 0.001}</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0.4636811131091502</v>
+        <v>0.4981334979664378</v>
       </c>
       <c r="G16" t="n">
-        <v>218.589460595562</v>
+        <v>223.2690765553185</v>
       </c>
       <c r="H16" t="n">
-        <v>134772.5191948981</v>
+        <v>126114.9186274323</v>
       </c>
       <c r="I16" t="n">
-        <v>367.1137687351131</v>
+        <v>355.1266233717663</v>
       </c>
       <c r="J16" t="n">
-        <v>43.25870436065651</v>
+        <v>52.60429690362638</v>
       </c>
       <c r="K16" t="n">
         <v>48192</v>
@@ -1370,7 +1370,7 @@
         <v>9639</v>
       </c>
       <c r="N16" t="n">
-        <v>4641.420962095261</v>
+        <v>2984.08509683609</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>-155.7501919400343</v>
+        <v>-158.2560504132112</v>
       </c>
     </row>
   </sheetData>
